--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>98245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B3" t="n">
-        <v>98243</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126181167</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B2" t="n">
-        <v>98245</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>98245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126179609</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126181167</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>98253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B3" t="n">
-        <v>98253</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126179029</v>
       </c>
       <c r="B2" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126179029</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126179609</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126181291</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126181167</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126177994</v>
       </c>
       <c r="B6" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126177483</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45087-2022 artfynd.xlsx
+++ b/artfynd/A 45087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126179029</v>
+        <v>126179609</v>
       </c>
       <c r="B2" t="n">
-        <v>98265</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126179609</v>
+        <v>126179029</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>98265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
